--- a/arquivos/exemplo_2D_3D.xlsx
+++ b/arquivos/exemplo_2D_3D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anderson.oliveira5\Downloads\Automações\Simulador-home\arquivos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E952AB92-DDF2-4A74-AC4D-E11CA0B6A140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{58CDDE7D-ADF1-4D15-9DE0-4F93E418A1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4950,7 +4950,7 @@
       <c r="E1" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>775</v>
       </c>
       <c r="G1" s="1" t="s">
